--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N25_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N25_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>22.90106810210866</v>
+        <v>3.721423566592657</v>
       </c>
       <c r="D2" t="n">
-        <v>23.51076205211091</v>
+        <v>3.820498833468022</v>
       </c>
       <c r="E2" t="n">
-        <v>7.876649895622945</v>
+        <v>1.279955608038729</v>
       </c>
       <c r="F2" t="n">
-        <v>11.89343522692334</v>
+        <v>1.932683224375042</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.08502937372829</v>
+        <v>3.913817273230848</v>
       </c>
       <c r="D3" t="n">
-        <v>23.90622484612025</v>
+        <v>3.884761537494541</v>
       </c>
       <c r="E3" t="n">
-        <v>7.876649895622945</v>
+        <v>1.279955608038729</v>
       </c>
       <c r="F3" t="n">
-        <v>11.89343522692334</v>
+        <v>1.932683224375042</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.20685442150154</v>
+        <v>2.308613843494</v>
       </c>
       <c r="D4" t="n">
-        <v>14.87762415081444</v>
+        <v>2.417613924507347</v>
       </c>
       <c r="E4" t="n">
-        <v>7.876649895622945</v>
+        <v>1.279955608038729</v>
       </c>
       <c r="F4" t="n">
-        <v>11.89343522692334</v>
+        <v>1.932683224375042</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>10.2852046705743</v>
+        <v>1.671345758968324</v>
       </c>
       <c r="D5" t="n">
-        <v>10.76042077183609</v>
+        <v>1.748568375423364</v>
       </c>
       <c r="E5" t="n">
-        <v>7.876649895622945</v>
+        <v>1.279955608038729</v>
       </c>
       <c r="F5" t="n">
-        <v>11.89343522692334</v>
+        <v>1.932683224375042</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>4.32821638953963</v>
+        <v>0.70333516330019</v>
       </c>
       <c r="D6" t="n">
-        <v>4.519852292288639</v>
+        <v>0.7344759974969038</v>
       </c>
       <c r="E6" t="n">
-        <v>7.876649895622945</v>
+        <v>1.279955608038729</v>
       </c>
       <c r="F6" t="n">
-        <v>11.89343522692334</v>
+        <v>1.932683224375042</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>35.4237542383426</v>
+        <v>5.756360063730673</v>
       </c>
       <c r="D7" t="n">
-        <v>29.03956248809141</v>
+        <v>4.718928904314854</v>
       </c>
       <c r="E7" t="n">
-        <v>7.876649895622945</v>
+        <v>1.279955608038729</v>
       </c>
       <c r="F7" t="n">
-        <v>11.89343522692334</v>
+        <v>1.932683224375042</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>24.79320626505841</v>
+        <v>4.028896018071991</v>
       </c>
       <c r="D8" t="n">
-        <v>28.54232099213668</v>
+        <v>4.638127161222211</v>
       </c>
       <c r="E8" t="n">
-        <v>7.876649895622945</v>
+        <v>1.279955608038729</v>
       </c>
       <c r="F8" t="n">
-        <v>11.89343522692334</v>
+        <v>1.932683224375042</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>21.08753724922148</v>
+        <v>3.42672480299849</v>
       </c>
       <c r="D9" t="n">
-        <v>20.94450674790812</v>
+        <v>3.40348234653507</v>
       </c>
       <c r="E9" t="n">
-        <v>7.876649895622945</v>
+        <v>1.279955608038729</v>
       </c>
       <c r="F9" t="n">
-        <v>11.89343522692334</v>
+        <v>1.932683224375042</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>20.24340763507767</v>
+        <v>3.289553740700121</v>
       </c>
       <c r="D10" t="n">
-        <v>19.2232175104682</v>
+        <v>3.123772845451083</v>
       </c>
       <c r="E10" t="n">
-        <v>7.876649895622945</v>
+        <v>1.279955608038729</v>
       </c>
       <c r="F10" t="n">
-        <v>11.89343522692334</v>
+        <v>1.932683224375042</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>16.49507126209744</v>
+        <v>2.680449080090835</v>
       </c>
       <c r="D11" t="n">
-        <v>43.11370739695737</v>
+        <v>7.005977452005572</v>
       </c>
       <c r="E11" t="n">
-        <v>7.876649895622945</v>
+        <v>1.279955608038729</v>
       </c>
       <c r="F11" t="n">
-        <v>11.89343522692334</v>
+        <v>1.932683224375042</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>15.57427572562696</v>
+        <v>2.530819805414382</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77728554450587</v>
+        <v>7.438808900982203</v>
       </c>
       <c r="E12" t="n">
-        <v>7.876649895622945</v>
+        <v>1.279955608038729</v>
       </c>
       <c r="F12" t="n">
-        <v>11.89343522692334</v>
+        <v>1.932683224375042</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
